--- a/数学群_20260904.xlsx
+++ b/数学群_20260904.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luhui\Python\checkin_v2\WeChatTextExport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_9E7B35239D05431D713537D00117692522688EE9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9E7B35239D05431D713537F46957739123688EE9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
